--- a/data/spain/p6_deployment/data_preparation/df_emergency_fill.xlsx
+++ b/data/spain/p6_deployment/data_preparation/df_emergency_fill.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J20"/>
+  <dimension ref="A1:J32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -478,7 +478,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>MNr3HRkC</t>
+          <t>YN50iYWr</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -494,7 +494,7 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hA5zaJZp</t>
+          <t>h4pRxZHk</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -510,7 +510,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>IVonL9jm</t>
+          <t>n1v9mjW7</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -526,7 +526,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>OQqSjnv9</t>
+          <t>tQQLbGv9</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -542,7 +542,7 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>YcAFQVSP</t>
+          <t>vyy1kC1e</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -558,7 +558,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>WhAFMMRi</t>
+          <t>EJYZzDn2</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -574,7 +574,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>vJDNK0d4</t>
+          <t>xhKUdf9L</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -590,7 +590,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>QekfJmLa</t>
+          <t>GOO6q4Wr</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -606,7 +606,7 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>8KIT2SzJ</t>
+          <t>SM0npHPF</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -622,7 +622,7 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>E1Xs9lu2</t>
+          <t>OlferefS</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
@@ -638,7 +638,7 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>ITdtTrn2</t>
+          <t>0ns5XwtA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
@@ -654,7 +654,7 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>M3h3GWnS</t>
+          <t>CQ0ABdJj</t>
         </is>
       </c>
       <c r="B13" t="inlineStr"/>
@@ -670,7 +670,7 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Eax2EqHs</t>
+          <t>KhwykQ8L</t>
         </is>
       </c>
       <c r="B14" t="inlineStr"/>
@@ -686,7 +686,7 @@
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>KbKTWiX8</t>
+          <t>v1KiOZ2d</t>
         </is>
       </c>
       <c r="B15" t="inlineStr"/>
@@ -702,7 +702,7 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>ruUIA1G6</t>
+          <t>f92vnwe3</t>
         </is>
       </c>
       <c r="B16" t="inlineStr"/>
@@ -718,7 +718,7 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>hnqZAAAk</t>
+          <t>0Y1WIvRG</t>
         </is>
       </c>
       <c r="B17" t="inlineStr"/>
@@ -734,7 +734,7 @@
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>nDzACNof</t>
+          <t>8CpDVHAM</t>
         </is>
       </c>
       <c r="B18" t="inlineStr"/>
@@ -750,7 +750,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>QyafIhIF</t>
+          <t>4KmdZaBc</t>
         </is>
       </c>
       <c r="B19" t="inlineStr"/>
@@ -766,7 +766,7 @@
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>hO0nKEm3</t>
+          <t>hpMqQeYq</t>
         </is>
       </c>
       <c r="B20" t="inlineStr"/>
@@ -779,6 +779,198 @@
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
     </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>ChPK4l66</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>MNr3HRkC</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>hA5zaJZp</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>IVonL9jm</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr"/>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>YcAFQVSP</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr"/>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>OQqSjnv9</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr"/>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>WhAFMMRi</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr"/>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>vJDNK0d4</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr"/>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>QekfJmLa</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr"/>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>8KIT2SzJ</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr"/>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>E1Xs9lu2</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr"/>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>ITdtTrn2</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr"/>
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/spain/p6_deployment/data_preparation/df_emergency_fill.xlsx
+++ b/data/spain/p6_deployment/data_preparation/df_emergency_fill.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J20"/>
+  <dimension ref="A1:J30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -478,7 +478,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>MNr3HRkC</t>
+          <t>YN50iYWr</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -494,7 +494,7 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hA5zaJZp</t>
+          <t>h4pRxZHk</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -510,7 +510,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>IVonL9jm</t>
+          <t>n1v9mjW7</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -526,7 +526,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>OQqSjnv9</t>
+          <t>tQQLbGv9</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -542,7 +542,7 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>YcAFQVSP</t>
+          <t>vyy1kC1e</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -558,7 +558,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>WhAFMMRi</t>
+          <t>EJYZzDn2</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -574,7 +574,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>vJDNK0d4</t>
+          <t>xhKUdf9L</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -590,7 +590,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>QekfJmLa</t>
+          <t>GOO6q4Wr</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -606,7 +606,7 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>8KIT2SzJ</t>
+          <t>SM0npHPF</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -622,7 +622,7 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>E1Xs9lu2</t>
+          <t>OlferefS</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
@@ -638,7 +638,7 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>ITdtTrn2</t>
+          <t>0ns5XwtA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
@@ -654,7 +654,7 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>M3h3GWnS</t>
+          <t>CQ0ABdJj</t>
         </is>
       </c>
       <c r="B13" t="inlineStr"/>
@@ -670,7 +670,7 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Eax2EqHs</t>
+          <t>v1KiOZ2d</t>
         </is>
       </c>
       <c r="B14" t="inlineStr"/>
@@ -686,7 +686,7 @@
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>KbKTWiX8</t>
+          <t>KhwykQ8L</t>
         </is>
       </c>
       <c r="B15" t="inlineStr"/>
@@ -702,7 +702,7 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>ruUIA1G6</t>
+          <t>f92vnwe3</t>
         </is>
       </c>
       <c r="B16" t="inlineStr"/>
@@ -718,7 +718,7 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>hnqZAAAk</t>
+          <t>0Y1WIvRG</t>
         </is>
       </c>
       <c r="B17" t="inlineStr"/>
@@ -734,7 +734,7 @@
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>nDzACNof</t>
+          <t>8CpDVHAM</t>
         </is>
       </c>
       <c r="B18" t="inlineStr"/>
@@ -750,7 +750,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>QyafIhIF</t>
+          <t>4KmdZaBc</t>
         </is>
       </c>
       <c r="B19" t="inlineStr"/>
@@ -766,7 +766,7 @@
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>hO0nKEm3</t>
+          <t>hpMqQeYq</t>
         </is>
       </c>
       <c r="B20" t="inlineStr"/>
@@ -779,6 +779,166 @@
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
     </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>ChPK4l66</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>MNr3HRkC</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>hA5zaJZp</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>IVonL9jm</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr"/>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>YcAFQVSP</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr"/>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>OQqSjnv9</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr"/>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>WhAFMMRi</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr"/>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>vJDNK0d4</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr"/>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>QekfJmLa</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr"/>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>8KIT2SzJ</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr"/>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/spain/p6_deployment/data_preparation/df_emergency_fill.xlsx
+++ b/data/spain/p6_deployment/data_preparation/df_emergency_fill.xlsx
@@ -702,7 +702,7 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>f92vnwe3</t>
+          <t>0Y1WIvRG</t>
         </is>
       </c>
       <c r="B16" t="inlineStr"/>
@@ -718,7 +718,7 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>0Y1WIvRG</t>
+          <t>f92vnwe3</t>
         </is>
       </c>
       <c r="B17" t="inlineStr"/>

--- a/data/spain/p6_deployment/data_preparation/df_emergency_fill.xlsx
+++ b/data/spain/p6_deployment/data_preparation/df_emergency_fill.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J30"/>
+  <dimension ref="A1:J5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -478,7 +478,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>YN50iYWr</t>
+          <t>OQqSjnv9</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -494,7 +494,7 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>h4pRxZHk</t>
+          <t>YcAFQVSP</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -510,7 +510,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>n1v9mjW7</t>
+          <t>WhAFMMRi</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -526,7 +526,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>tQQLbGv9</t>
+          <t>vJDNK0d4</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -539,406 +539,6 @@
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
     </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>vyy1kC1e</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>EJYZzDn2</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>xhKUdf9L</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>GOO6q4Wr</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>SM0npHPF</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>OlferefS</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>0ns5XwtA</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>CQ0ABdJj</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>v1KiOZ2d</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>KhwykQ8L</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>0Y1WIvRG</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>f92vnwe3</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr"/>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>8CpDVHAM</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>4KmdZaBc</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>hpMqQeYq</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr"/>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>ChPK4l66</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr"/>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>MNr3HRkC</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr"/>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="inlineStr">
-        <is>
-          <t>hA5zaJZp</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr"/>
-      <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="inlineStr">
-        <is>
-          <t>IVonL9jm</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr"/>
-      <c r="C24" t="inlineStr"/>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>YcAFQVSP</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr"/>
-      <c r="C25" t="inlineStr"/>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="1" t="inlineStr">
-        <is>
-          <t>OQqSjnv9</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr"/>
-      <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="1" t="inlineStr">
-        <is>
-          <t>WhAFMMRi</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr"/>
-      <c r="C27" t="inlineStr"/>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="1" t="inlineStr">
-        <is>
-          <t>vJDNK0d4</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr"/>
-      <c r="C28" t="inlineStr"/>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="1" t="inlineStr">
-        <is>
-          <t>QekfJmLa</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr"/>
-      <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="1" t="inlineStr">
-        <is>
-          <t>8KIT2SzJ</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr"/>
-      <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/spain/p6_deployment/data_preparation/df_emergency_fill.xlsx
+++ b/data/spain/p6_deployment/data_preparation/df_emergency_fill.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,40 +436,25 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>mean_last_match_mean_rat_player_start_home_against</t>
+          <t>mean_last_match_mean_rat_player_start_away_against</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>mean_last_match_mean_rat_player_start_away_against</t>
+          <t>dif_mean_rat_player_sub</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_rat_player_sub</t>
+          <t>dif_mean_int_rep_player_sub</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_int_rep_player_sub</t>
+          <t>dif_mean_hei_player_sub</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_val_player_sub</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_sub</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_sub</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_age_player_sub</t>
         </is>
@@ -478,7 +463,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>OQqSjnv9</t>
+          <t>YN50iYWr</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -487,14 +472,11 @@
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>YcAFQVSP</t>
+          <t>h4pRxZHk</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -503,14 +485,11 @@
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>WhAFMMRi</t>
+          <t>n1v9mjW7</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -519,14 +498,11 @@
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>vJDNK0d4</t>
+          <t>tQQLbGv9</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -535,9 +511,253 @@
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>vyy1kC1e</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>EJYZzDn2</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>xhKUdf9L</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>GOO6q4Wr</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>SM0npHPF</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>OlferefS</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>0ns5XwtA</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>CQ0ABdJj</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>KhwykQ8L</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>v1KiOZ2d</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>f92vnwe3</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>0Y1WIvRG</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>8CpDVHAM</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>4KmdZaBc</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>hpMqQeYq</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>ChPK4l66</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>MNr3HRkC</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>hA5zaJZp</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>IVonL9jm</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr"/>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/spain/p6_deployment/data_preparation/df_emergency_fill.xlsx
+++ b/data/spain/p6_deployment/data_preparation/df_emergency_fill.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -528,7 +528,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>EJYZzDn2</t>
+          <t>xhKUdf9L</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -541,7 +541,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>xhKUdf9L</t>
+          <t>EJYZzDn2</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -619,7 +619,7 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>KhwykQ8L</t>
+          <t>v1KiOZ2d</t>
         </is>
       </c>
       <c r="B14" t="inlineStr"/>
@@ -632,7 +632,7 @@
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>v1KiOZ2d</t>
+          <t>KhwykQ8L</t>
         </is>
       </c>
       <c r="B15" t="inlineStr"/>
@@ -707,58 +707,6 @@
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr"/>
     </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>ChPK4l66</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr"/>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>MNr3HRkC</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr"/>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="inlineStr">
-        <is>
-          <t>hA5zaJZp</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr"/>
-      <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="inlineStr">
-        <is>
-          <t>IVonL9jm</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr"/>
-      <c r="C24" t="inlineStr"/>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/spain/p6_deployment/data_preparation/df_emergency_fill.xlsx
+++ b/data/spain/p6_deployment/data_preparation/df_emergency_fill.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -502,7 +502,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>tQQLbGv9</t>
+          <t>vyy1kC1e</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -515,7 +515,7 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>vyy1kC1e</t>
+          <t>tQQLbGv9</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -528,7 +528,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>xhKUdf9L</t>
+          <t>EJYZzDn2</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -541,7 +541,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>EJYZzDn2</t>
+          <t>xhKUdf9L</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -619,7 +619,7 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>v1KiOZ2d</t>
+          <t>KhwykQ8L</t>
         </is>
       </c>
       <c r="B14" t="inlineStr"/>
@@ -632,7 +632,7 @@
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>KhwykQ8L</t>
+          <t>v1KiOZ2d</t>
         </is>
       </c>
       <c r="B15" t="inlineStr"/>
@@ -645,7 +645,7 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>f92vnwe3</t>
+          <t>0Y1WIvRG</t>
         </is>
       </c>
       <c r="B16" t="inlineStr"/>
@@ -658,7 +658,7 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>0Y1WIvRG</t>
+          <t>f92vnwe3</t>
         </is>
       </c>
       <c r="B17" t="inlineStr"/>
@@ -668,45 +668,6 @@
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr"/>
     </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>8CpDVHAM</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>4KmdZaBc</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>hpMqQeYq</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr"/>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/spain/p6_deployment/data_preparation/df_emergency_fill.xlsx
+++ b/data/spain/p6_deployment/data_preparation/df_emergency_fill.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -528,7 +528,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>EJYZzDn2</t>
+          <t>xhKUdf9L</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -541,7 +541,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>xhKUdf9L</t>
+          <t>EJYZzDn2</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -590,84 +590,6 @@
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
     </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>0ns5XwtA</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>CQ0ABdJj</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>KhwykQ8L</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>v1KiOZ2d</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>0Y1WIvRG</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>f92vnwe3</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr"/>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/spain/p6_deployment/data_preparation/df_emergency_fill.xlsx
+++ b/data/spain/p6_deployment/data_preparation/df_emergency_fill.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -525,71 +525,6 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
     </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>xhKUdf9L</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>EJYZzDn2</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>GOO6q4Wr</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>SM0npHPF</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>OlferefS</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/spain/p6_deployment/data_preparation/df_emergency_fill.xlsx
+++ b/data/spain/p6_deployment/data_preparation/df_emergency_fill.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -463,7 +463,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>YN50iYWr</t>
+          <t>fVeJ32M5</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -476,7 +476,7 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>h4pRxZHk</t>
+          <t>SdHeBgOE</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -489,7 +489,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>n1v9mjW7</t>
+          <t>dzUhmsxP</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -502,7 +502,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>vyy1kC1e</t>
+          <t>na927pNt</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -515,7 +515,7 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>tQQLbGv9</t>
+          <t>SfxxiPx0</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -525,6 +525,71 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
     </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>jckS1tiI</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>8EcB5Oig</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>CjIFsr1e</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>08zpk37C</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>YeqTho8m</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/spain/p6_deployment/data_preparation/df_emergency_fill.xlsx
+++ b/data/spain/p6_deployment/data_preparation/df_emergency_fill.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -463,7 +463,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>fVeJ32M5</t>
+          <t>f5SjRHyR</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -476,7 +476,7 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>SdHeBgOE</t>
+          <t>rkN7RQV9</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -489,7 +489,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>dzUhmsxP</t>
+          <t>bwZsTw7E</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -502,7 +502,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>na927pNt</t>
+          <t>445r4WXo</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -515,7 +515,7 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>SfxxiPx0</t>
+          <t>QiF6bS1N</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -528,7 +528,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>jckS1tiI</t>
+          <t>pxdwg6Pp</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -541,7 +541,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>8EcB5Oig</t>
+          <t>OAmz0KLU</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -554,7 +554,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>CjIFsr1e</t>
+          <t>dCNk2A2b</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -567,7 +567,7 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>08zpk37C</t>
+          <t>ImLNuMV7</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -580,7 +580,7 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>YeqTho8m</t>
+          <t>xWrPG9Hi</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
@@ -590,6 +590,214 @@
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
     </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>4b2YCRGG</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>dYbQEmn4</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>IRBb0lXA</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>xjut9IFr</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>8b5vHIeT</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>AyPaTn1c</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>fVeJ32M5</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>SdHeBgOE</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>dzUhmsxP</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>na927pNt</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>SfxxiPx0</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>jckS1tiI</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>8EcB5Oig</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr"/>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>CjIFsr1e</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr"/>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>08zpk37C</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr"/>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>YeqTho8m</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr"/>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/spain/p6_deployment/data_preparation/df_emergency_fill.xlsx
+++ b/data/spain/p6_deployment/data_preparation/df_emergency_fill.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -463,7 +463,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>f5SjRHyR</t>
+          <t>AyPaTn1c</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -476,7 +476,7 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>rkN7RQV9</t>
+          <t>fVeJ32M5</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -489,7 +489,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>bwZsTw7E</t>
+          <t>SdHeBgOE</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -502,7 +502,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>445r4WXo</t>
+          <t>dzUhmsxP</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -515,7 +515,7 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>QiF6bS1N</t>
+          <t>na927pNt</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -528,7 +528,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>pxdwg6Pp</t>
+          <t>SfxxiPx0</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -538,266 +538,6 @@
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
     </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>OAmz0KLU</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>dCNk2A2b</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>ImLNuMV7</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>xWrPG9Hi</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>4b2YCRGG</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>dYbQEmn4</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>IRBb0lXA</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>xjut9IFr</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>8b5vHIeT</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>AyPaTn1c</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr"/>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>fVeJ32M5</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>SdHeBgOE</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>dzUhmsxP</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr"/>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>na927pNt</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr"/>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>SfxxiPx0</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr"/>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="inlineStr">
-        <is>
-          <t>jckS1tiI</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr"/>
-      <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="inlineStr">
-        <is>
-          <t>8EcB5Oig</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr"/>
-      <c r="C24" t="inlineStr"/>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>CjIFsr1e</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr"/>
-      <c r="C25" t="inlineStr"/>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="1" t="inlineStr">
-        <is>
-          <t>08zpk37C</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr"/>
-      <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="1" t="inlineStr">
-        <is>
-          <t>YeqTho8m</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr"/>
-      <c r="C27" t="inlineStr"/>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/spain/p6_deployment/data_preparation/df_emergency_fill.xlsx
+++ b/data/spain/p6_deployment/data_preparation/df_emergency_fill.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -463,7 +463,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>AyPaTn1c</t>
+          <t>YJVCWCD6</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -476,7 +476,7 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>fVeJ32M5</t>
+          <t>n37VJZT0</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -489,7 +489,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>SdHeBgOE</t>
+          <t>4rQsoH7m</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -502,7 +502,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>dzUhmsxP</t>
+          <t>jyEMLeal</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -515,7 +515,7 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>na927pNt</t>
+          <t>h0AwIDbD</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -528,7 +528,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>SfxxiPx0</t>
+          <t>4vvdzeEs</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -538,6 +538,331 @@
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
     </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>YemQuHjK</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>KSw0hfzQ</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hMoEUjrJ</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>06X4YYrf</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>pGrl7dpe</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>6VWd5zF7</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>bqbA3PNE</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>QDjsB5oT</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>ddsD5q9j</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>f5SjRHyR</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>rkN7RQV9</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>bwZsTw7E</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>445r4WXo</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>QiF6bS1N</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>pxdwg6Pp</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>OAmz0KLU</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>dCNk2A2b</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr"/>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>ImLNuMV7</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr"/>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>xWrPG9Hi</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr"/>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>4b2YCRGG</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr"/>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>dYbQEmn4</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr"/>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>IRBb0lXA</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr"/>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>xjut9IFr</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr"/>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>8b5vHIeT</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr"/>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>AyPaTn1c</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr"/>
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/spain/p6_deployment/data_preparation/df_emergency_fill.xlsx
+++ b/data/spain/p6_deployment/data_preparation/df_emergency_fill.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G32"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -463,7 +463,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>YJVCWCD6</t>
+          <t>445r4WXo</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -476,7 +476,7 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>n37VJZT0</t>
+          <t>QiF6bS1N</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -489,7 +489,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>4rQsoH7m</t>
+          <t>pxdwg6Pp</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -502,7 +502,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>jyEMLeal</t>
+          <t>OAmz0KLU</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -515,7 +515,7 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>h0AwIDbD</t>
+          <t>dCNk2A2b</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -528,7 +528,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>4vvdzeEs</t>
+          <t>ImLNuMV7</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -541,7 +541,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>YemQuHjK</t>
+          <t>xWrPG9Hi</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -554,7 +554,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>KSw0hfzQ</t>
+          <t>4b2YCRGG</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -567,7 +567,7 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>hMoEUjrJ</t>
+          <t>dYbQEmn4</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -577,292 +577,6 @@
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr"/>
     </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>06X4YYrf</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>pGrl7dpe</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>6VWd5zF7</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>bqbA3PNE</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>QDjsB5oT</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>ddsD5q9j</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>f5SjRHyR</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr"/>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>rkN7RQV9</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>bwZsTw7E</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>445r4WXo</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr"/>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>QiF6bS1N</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr"/>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>pxdwg6Pp</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr"/>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="inlineStr">
-        <is>
-          <t>OAmz0KLU</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr"/>
-      <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="inlineStr">
-        <is>
-          <t>dCNk2A2b</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr"/>
-      <c r="C24" t="inlineStr"/>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>ImLNuMV7</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr"/>
-      <c r="C25" t="inlineStr"/>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="1" t="inlineStr">
-        <is>
-          <t>xWrPG9Hi</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr"/>
-      <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="1" t="inlineStr">
-        <is>
-          <t>4b2YCRGG</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr"/>
-      <c r="C27" t="inlineStr"/>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="1" t="inlineStr">
-        <is>
-          <t>dYbQEmn4</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr"/>
-      <c r="C28" t="inlineStr"/>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="1" t="inlineStr">
-        <is>
-          <t>IRBb0lXA</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr"/>
-      <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="1" t="inlineStr">
-        <is>
-          <t>xjut9IFr</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr"/>
-      <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="1" t="inlineStr">
-        <is>
-          <t>8b5vHIeT</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr"/>
-      <c r="C31" t="inlineStr"/>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="1" t="inlineStr">
-        <is>
-          <t>AyPaTn1c</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr"/>
-      <c r="C32" t="inlineStr"/>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/spain/p6_deployment/data_preparation/df_emergency_fill.xlsx
+++ b/data/spain/p6_deployment/data_preparation/df_emergency_fill.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,17 +436,17 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>mean_last_match_mean_rat_player_start_away_against</t>
+          <t>mean_last_180_matches_mean_rat_player_start_home_against</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>mean_last_180_matches_mean_rat_player_start_away_against</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_rat_player_sub</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_sub</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -463,7 +463,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>AyPaTn1c</t>
+          <t>CvbDaBsg</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -476,7 +476,7 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>fVeJ32M5</t>
+          <t>YgnMckC5</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -489,7 +489,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>SdHeBgOE</t>
+          <t>hzRnqjcC</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -502,7 +502,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>dzUhmsxP</t>
+          <t>4Ef51XCt</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -515,7 +515,7 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>na927pNt</t>
+          <t>CQIvoCSa</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -528,7 +528,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>SfxxiPx0</t>
+          <t>EB22wLQj</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -538,6 +538,305 @@
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
     </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>KApUeTtI</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>40FWnYcm</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>0AJjqex0</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>QmPfsURO</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>YJVCWCD6</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>n37VJZT0</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>4rQsoH7m</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>jyEMLeal</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>h0AwIDbD</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>4vvdzeEs</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>YemQuHjK</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>KSw0hfzQ</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>hMoEUjrJ</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>06X4YYrf</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>pGrl7dpe</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>6VWd5zF7</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>bqbA3PNE</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr"/>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>QDjsB5oT</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr"/>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>ddsD5q9j</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr"/>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>f5SjRHyR</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr"/>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>bwZsTw7E</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr"/>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>rkN7RQV9</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr"/>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>445r4WXo</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr"/>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/spain/p6_deployment/data_preparation/df_emergency_fill.xlsx
+++ b/data/spain/p6_deployment/data_preparation/df_emergency_fill.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -463,7 +463,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>CvbDaBsg</t>
+          <t>pGrl7dpe</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -476,7 +476,7 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>YgnMckC5</t>
+          <t>bqbA3PNE</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -489,7 +489,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hzRnqjcC</t>
+          <t>6VWd5zF7</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -502,7 +502,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>4Ef51XCt</t>
+          <t>QDjsB5oT</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -515,7 +515,7 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>CQIvoCSa</t>
+          <t>ddsD5q9j</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -528,7 +528,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>EB22wLQj</t>
+          <t>f5SjRHyR</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -541,7 +541,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>KApUeTtI</t>
+          <t>rkN7RQV9</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -554,7 +554,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>40FWnYcm</t>
+          <t>bwZsTw7E</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -564,279 +564,6 @@
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr"/>
     </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>0AJjqex0</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>QmPfsURO</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>YJVCWCD6</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>n37VJZT0</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>4rQsoH7m</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>jyEMLeal</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>h0AwIDbD</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>4vvdzeEs</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr"/>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>YemQuHjK</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>KSw0hfzQ</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>hMoEUjrJ</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr"/>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>06X4YYrf</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr"/>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>pGrl7dpe</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr"/>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="inlineStr">
-        <is>
-          <t>6VWd5zF7</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr"/>
-      <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="inlineStr">
-        <is>
-          <t>bqbA3PNE</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr"/>
-      <c r="C24" t="inlineStr"/>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>QDjsB5oT</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr"/>
-      <c r="C25" t="inlineStr"/>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="1" t="inlineStr">
-        <is>
-          <t>ddsD5q9j</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr"/>
-      <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="1" t="inlineStr">
-        <is>
-          <t>f5SjRHyR</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr"/>
-      <c r="C27" t="inlineStr"/>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="1" t="inlineStr">
-        <is>
-          <t>bwZsTw7E</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr"/>
-      <c r="C28" t="inlineStr"/>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="1" t="inlineStr">
-        <is>
-          <t>rkN7RQV9</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr"/>
-      <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="1" t="inlineStr">
-        <is>
-          <t>445r4WXo</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr"/>
-      <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/spain/p6_deployment/data_preparation/df_emergency_fill.xlsx
+++ b/data/spain/p6_deployment/data_preparation/df_emergency_fill.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -463,7 +463,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>CvbDaBsg</t>
+          <t>n37VJZT0</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -476,7 +476,7 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>YgnMckC5</t>
+          <t>4rQsoH7m</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -489,7 +489,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hzRnqjcC</t>
+          <t>jyEMLeal</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -502,7 +502,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>4Ef51XCt</t>
+          <t>h0AwIDbD</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -515,7 +515,7 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>CQIvoCSa</t>
+          <t>4vvdzeEs</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -528,7 +528,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>EB22wLQj</t>
+          <t>YemQuHjK</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -541,7 +541,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>KApUeTtI</t>
+          <t>KSw0hfzQ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -554,7 +554,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>40FWnYcm</t>
+          <t>hMoEUjrJ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -567,7 +567,7 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>0AJjqex0</t>
+          <t>06X4YYrf</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -577,266 +577,6 @@
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr"/>
     </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>QmPfsURO</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>YJVCWCD6</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>n37VJZT0</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>4rQsoH7m</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>jyEMLeal</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>h0AwIDbD</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>4vvdzeEs</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr"/>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>YemQuHjK</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>KSw0hfzQ</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>hMoEUjrJ</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr"/>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>06X4YYrf</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr"/>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>pGrl7dpe</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr"/>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="inlineStr">
-        <is>
-          <t>6VWd5zF7</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr"/>
-      <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="inlineStr">
-        <is>
-          <t>bqbA3PNE</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr"/>
-      <c r="C24" t="inlineStr"/>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>QDjsB5oT</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr"/>
-      <c r="C25" t="inlineStr"/>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="1" t="inlineStr">
-        <is>
-          <t>ddsD5q9j</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr"/>
-      <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="1" t="inlineStr">
-        <is>
-          <t>f5SjRHyR</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr"/>
-      <c r="C27" t="inlineStr"/>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="1" t="inlineStr">
-        <is>
-          <t>bwZsTw7E</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr"/>
-      <c r="C28" t="inlineStr"/>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="1" t="inlineStr">
-        <is>
-          <t>rkN7RQV9</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr"/>
-      <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="1" t="inlineStr">
-        <is>
-          <t>445r4WXo</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr"/>
-      <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/spain/p6_deployment/data_preparation/df_emergency_fill.xlsx
+++ b/data/spain/p6_deployment/data_preparation/df_emergency_fill.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -463,7 +463,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>n37VJZT0</t>
+          <t>YJVCWCD6</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -476,7 +476,7 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>4rQsoH7m</t>
+          <t>n37VJZT0</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -489,7 +489,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>jyEMLeal</t>
+          <t>4rQsoH7m</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -502,7 +502,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>h0AwIDbD</t>
+          <t>jyEMLeal</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -515,7 +515,7 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>4vvdzeEs</t>
+          <t>h0AwIDbD</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -525,58 +525,6 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
     </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>YemQuHjK</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>KSw0hfzQ</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>hMoEUjrJ</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>06X4YYrf</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/spain/p6_deployment/data_preparation/df_emergency_fill.xlsx
+++ b/data/spain/p6_deployment/data_preparation/df_emergency_fill.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,73 +436,95 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>mean_last_180_matches_mean_rat_player_start_home_against</t>
+          <t>dif_mean_last_180_matches_mean_rat_player_start_against</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>mean_last_180_matches_mean_rat_player_start_away_against</t>
+          <t>dif_mean_hei_player_sub</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_age_player_miss</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_sub</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_value_player_start</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_rat_player_sub</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_sub</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_sub</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>YJVCWCD6</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr"/>
+          <t>ll7vCuXF</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>1</v>
+      </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
+      <c r="E2" t="n">
+        <v>-0.4314007377642196</v>
+      </c>
       <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
+      <c r="G2" t="n">
+        <v>0.08177452209805446</v>
+      </c>
+      <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>n37VJZT0</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr"/>
+          <t>YNHbsZ6C</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>1</v>
+      </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
+      <c r="E3" t="n">
+        <v>-0.4314007377642196</v>
+      </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>4rQsoH7m</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr"/>
+          <t>Gz9WD123</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>1</v>
+      </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
+      <c r="E4" t="n">
+        <v>-0.4314007377642196</v>
+      </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>jyEMLeal</t>
+          <t>CvbDaBsg</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -511,19 +533,151 @@
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>h0AwIDbD</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr"/>
+          <t>YgnMckC5</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1</v>
+      </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
+      <c r="G6" t="n">
+        <v>0.08177452209805446</v>
+      </c>
+      <c r="H6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>hzRnqjcC</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="n">
+        <v>-0.4314007377642196</v>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>4Ef51XCt</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>CQIvoCSa</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>KApUeTtI</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>EB22wLQj</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>40FWnYcm</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="n">
+        <v>-0.4314007377642196</v>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>0AJjqex0</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>QmPfsURO</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.04545428873891213</v>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="n">
+        <v>0.08177452209805446</v>
+      </c>
+      <c r="H14" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/spain/p6_deployment/data_preparation/df_emergency_fill.xlsx
+++ b/data/spain/p6_deployment/data_preparation/df_emergency_fill.xlsx
@@ -468,7 +468,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>ll7vCuXF</t>
+          <t>2Xrca2mA</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -477,18 +477,18 @@
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="n">
-        <v>-0.4314007377642196</v>
+        <v>-0.7132575737233142</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="n">
-        <v>0.08177452209805446</v>
+        <v>-0.4205251519600463</v>
       </c>
       <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>YNHbsZ6C</t>
+          <t>f1xuAJ1S</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -497,7 +497,7 @@
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="n">
-        <v>-0.4314007377642196</v>
+        <v>-0.7132575737233142</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
@@ -506,31 +506,39 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Gz9WD123</t>
+          <t>65kl1OIc</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>1</v>
       </c>
-      <c r="C4" t="inlineStr"/>
+      <c r="C4" t="n">
+        <v>0.3146098042699321</v>
+      </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="n">
-        <v>-0.4314007377642196</v>
+        <v>-0.7132575737233142</v>
       </c>
       <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
+      <c r="G4" t="n">
+        <v>-0.4205251519600463</v>
+      </c>
       <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>CvbDaBsg</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr"/>
+          <t>0SQqjbAd</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>1</v>
+      </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
+      <c r="E5" t="n">
+        <v>-0.7132575737233142</v>
+      </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
@@ -538,7 +546,7 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>YgnMckC5</t>
+          <t>8Uo5ctIM</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -546,17 +554,17 @@
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
+      <c r="E6" t="n">
+        <v>-0.7132575737233142</v>
+      </c>
       <c r="F6" t="inlineStr"/>
-      <c r="G6" t="n">
-        <v>0.08177452209805446</v>
-      </c>
+      <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hzRnqjcC</t>
+          <t>h2NyhKup</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -565,7 +573,7 @@
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="n">
-        <v>-0.4314007377642196</v>
+        <v>-0.7132575737233142</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
@@ -574,27 +582,37 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>4Ef51XCt</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr"/>
+          <t>ll7vCuXF</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1</v>
+      </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
+      <c r="E8" t="n">
+        <v>-0.7132575737233142</v>
+      </c>
       <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
+      <c r="G8" t="n">
+        <v>-0.4205251519600463</v>
+      </c>
       <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>CQIvoCSa</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr"/>
+          <t>YNHbsZ6C</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1</v>
+      </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
+      <c r="E9" t="n">
+        <v>-0.7132575737233142</v>
+      </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
@@ -602,13 +620,17 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>KApUeTtI</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr"/>
+          <t>Gz9WD123</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1</v>
+      </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
+      <c r="E10" t="n">
+        <v>-0.7132575737233142</v>
+      </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
@@ -616,7 +638,7 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>EB22wLQj</t>
+          <t>CvbDaBsg</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
@@ -630,7 +652,7 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>40FWnYcm</t>
+          <t>YgnMckC5</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -638,23 +660,27 @@
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
-      <c r="E12" t="n">
-        <v>-0.4314007377642196</v>
-      </c>
+      <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
+      <c r="G12" t="n">
+        <v>-0.4205251519600463</v>
+      </c>
       <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>0AJjqex0</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr"/>
+          <t>hzRnqjcC</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1</v>
+      </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
+      <c r="E13" t="n">
+        <v>-0.7132575737233142</v>
+      </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
@@ -662,21 +688,15 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>QmPfsURO</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>1</v>
-      </c>
-      <c r="C14" t="n">
-        <v>0.04545428873891213</v>
-      </c>
+          <t>4Ef51XCt</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr"/>
-      <c r="G14" t="n">
-        <v>0.08177452209805446</v>
-      </c>
+      <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
     </row>
   </sheetData>

--- a/data/spain/p6_deployment/data_preparation/df_emergency_fill.xlsx
+++ b/data/spain/p6_deployment/data_preparation/df_emergency_fill.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,204 +441,178 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_hei_player_sub</t>
+          <t>dif_mean_age_player_sub</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_age_player_miss</t>
+          <t>dif_mean_rat_player_sub</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_age_player_sub</t>
+          <t>dif_mean_value_player_sub</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_value_player_start</t>
+          <t>dif_mean_pot_player_sub</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_rat_player_sub</t>
+          <t>dif_mean_wage_player_sub</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rep_player_sub</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>2Xrca2mA</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>1</v>
-      </c>
+          <t>E595Qvn9</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
-      <c r="E2" t="n">
-        <v>-0.7132575737233142</v>
-      </c>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
-      <c r="G2" t="n">
-        <v>-0.4205251519600463</v>
-      </c>
+      <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>f1xuAJ1S</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>1</v>
-      </c>
+          <t>jiAoNQdE</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
-      <c r="E3" t="n">
-        <v>-0.7132575737233142</v>
-      </c>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>65kl1OIc</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>1</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0.3146098042699321</v>
-      </c>
+          <t>842EOIGL</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
-      <c r="E4" t="n">
-        <v>-0.7132575737233142</v>
-      </c>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
-      <c r="G4" t="n">
-        <v>-0.4205251519600463</v>
-      </c>
+      <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>0SQqjbAd</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>1</v>
-      </c>
+          <t>naHJ2yf2</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
-      <c r="E5" t="n">
-        <v>-0.7132575737233142</v>
-      </c>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>8Uo5ctIM</t>
+          <t>02sgHz9e</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>1</v>
       </c>
-      <c r="C6" t="inlineStr"/>
+      <c r="C6" t="n">
+        <v>0.1389048195692081</v>
+      </c>
       <c r="D6" t="inlineStr"/>
-      <c r="E6" t="n">
-        <v>-0.7132575737233142</v>
-      </c>
+      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>h2NyhKup</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>1</v>
-      </c>
+          <t>4zlpJdvq</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr"/>
-      <c r="E7" t="n">
-        <v>-0.7132575737233142</v>
-      </c>
+      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>ll7vCuXF</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>1</v>
-      </c>
+          <t>8Sp1FEw8</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr"/>
-      <c r="E8" t="n">
-        <v>-0.7132575737233142</v>
-      </c>
+      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
-      <c r="G8" t="n">
-        <v>-0.4205251519600463</v>
-      </c>
+      <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>YNHbsZ6C</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>1</v>
-      </c>
+          <t>dhkQFrkl</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
-      <c r="E9" t="n">
-        <v>-0.7132575737233142</v>
-      </c>
+      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Gz9WD123</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>1</v>
-      </c>
+          <t>x88gL4RQ</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr"/>
-      <c r="E10" t="n">
-        <v>-0.7132575737233142</v>
-      </c>
+      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>CvbDaBsg</t>
+          <t>vymauDyP</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
@@ -648,47 +622,42 @@
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>YgnMckC5</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>1</v>
-      </c>
+          <t>QqTA4cPk</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
-      <c r="G12" t="n">
-        <v>-0.4205251519600463</v>
-      </c>
+      <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>hzRnqjcC</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>1</v>
-      </c>
+          <t>2Xrca2mA</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
-      <c r="E13" t="n">
-        <v>-0.7132575737233142</v>
-      </c>
+      <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>4Ef51XCt</t>
+          <t>f1xuAJ1S</t>
         </is>
       </c>
       <c r="B14" t="inlineStr"/>
@@ -698,6 +667,116 @@
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>65kl1OIc</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.1389048195692081</v>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>0SQqjbAd</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>8Uo5ctIM</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>h2NyhKup</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>ll7vCuXF</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>YNHbsZ6C</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>Gz9WD123</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/spain/p6_deployment/data_preparation/df_emergency_fill.xlsx
+++ b/data/spain/p6_deployment/data_preparation/df_emergency_fill.xlsx
@@ -540,7 +540,7 @@
         <v>1</v>
       </c>
       <c r="C6" t="n">
-        <v>0.1389048195692081</v>
+        <v>0.1380230300720776</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
@@ -679,7 +679,7 @@
         <v>1</v>
       </c>
       <c r="C15" t="n">
-        <v>0.1389048195692081</v>
+        <v>0.1380230300720776</v>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr"/>

--- a/data/spain/p6_deployment/data_preparation/df_emergency_fill.xlsx
+++ b/data/spain/p6_deployment/data_preparation/df_emergency_fill.xlsx
@@ -540,7 +540,7 @@
         <v>1</v>
       </c>
       <c r="C6" t="n">
-        <v>0.1380230300720776</v>
+        <v>0.1379293158038532</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
@@ -679,7 +679,7 @@
         <v>1</v>
       </c>
       <c r="C15" t="n">
-        <v>0.1380230300720776</v>
+        <v>0.1379293158038532</v>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr"/>

--- a/data/spain/p6_deployment/data_preparation/df_emergency_fill.xlsx
+++ b/data/spain/p6_deployment/data_preparation/df_emergency_fill.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,7 +473,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>E595Qvn9</t>
+          <t>QqTA4cPk</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -488,7 +488,7 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>jiAoNQdE</t>
+          <t>2Xrca2mA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -503,7 +503,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>842EOIGL</t>
+          <t>f1xuAJ1S</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -518,11 +518,15 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>naHJ2yf2</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
+          <t>65kl1OIc</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.3030425709125815</v>
+      </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
@@ -533,15 +537,11 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>02sgHz9e</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>1</v>
-      </c>
-      <c r="C6" t="n">
-        <v>0.1379293158038532</v>
-      </c>
+          <t>0SQqjbAd</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
@@ -549,235 +549,6 @@
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
     </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>4zlpJdvq</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>8Sp1FEw8</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>dhkQFrkl</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>x88gL4RQ</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>vymauDyP</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>QqTA4cPk</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>2Xrca2mA</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>f1xuAJ1S</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>65kl1OIc</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>1</v>
-      </c>
-      <c r="C15" t="n">
-        <v>0.1379293158038532</v>
-      </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>0SQqjbAd</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>8Uo5ctIM</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr"/>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>h2NyhKup</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>ll7vCuXF</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>YNHbsZ6C</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr"/>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>Gz9WD123</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr"/>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/spain/p6_deployment/data_preparation/df_emergency_fill.xlsx
+++ b/data/spain/p6_deployment/data_preparation/df_emergency_fill.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,7 +461,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_wage_player_sub</t>
+          <t>dif_mean_hei_player_sub</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -473,7 +473,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>QqTA4cPk</t>
+          <t>zeCiJHet</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -488,11 +488,15 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>2Xrca2mA</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
+          <t>U5mYDMJ0</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.05628319734897231</v>
+      </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
@@ -503,7 +507,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>f1xuAJ1S</t>
+          <t>rsizUY9b</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -518,15 +522,11 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>65kl1OIc</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>1</v>
-      </c>
-      <c r="C5" t="n">
-        <v>0.3030425709125815</v>
-      </c>
+          <t>UaS8aGMt</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
@@ -537,7 +537,7 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>0SQqjbAd</t>
+          <t>QXtsC0lD</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -549,6 +549,231 @@
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
     </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>zHmSVfun</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>YFePBifU</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>dA00HeQh</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>4z48FZf5</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>02cHDDPH</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>E595Qvn9</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>jiAoNQdE</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>842EOIGL</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>naHJ2yf2</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>02sgHz9e</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>4zlpJdvq</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>8Sp1FEw8</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>dhkQFrkl</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>x88gL4RQ</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>vymauDyP</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/spain/p6_deployment/data_preparation/df_emergency_fill.xlsx
+++ b/data/spain/p6_deployment/data_preparation/df_emergency_fill.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,7 +473,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>zeCiJHet</t>
+          <t>E595Qvn9</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -488,15 +488,11 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>U5mYDMJ0</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C3" t="n">
-        <v>0.05628319734897231</v>
-      </c>
+          <t>jiAoNQdE</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
@@ -507,7 +503,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>rsizUY9b</t>
+          <t>842EOIGL</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -522,7 +518,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>UaS8aGMt</t>
+          <t>naHJ2yf2</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -537,7 +533,7 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>QXtsC0lD</t>
+          <t>02sgHz9e</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -552,7 +548,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>zHmSVfun</t>
+          <t>4zlpJdvq</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -567,7 +563,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>YFePBifU</t>
+          <t>8Sp1FEw8</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -582,7 +578,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>dA00HeQh</t>
+          <t>dhkQFrkl</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -597,7 +593,7 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>4z48FZf5</t>
+          <t>x88gL4RQ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -612,7 +608,7 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>02cHDDPH</t>
+          <t>vymauDyP</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
@@ -624,156 +620,6 @@
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
     </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>E595Qvn9</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>jiAoNQdE</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>842EOIGL</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>naHJ2yf2</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>02sgHz9e</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>4zlpJdvq</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr"/>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>8Sp1FEw8</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>dhkQFrkl</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>x88gL4RQ</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr"/>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>vymauDyP</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr"/>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/spain/p6_deployment/data_preparation/df_emergency_fill.xlsx
+++ b/data/spain/p6_deployment/data_preparation/df_emergency_fill.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,7 +473,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>E595Qvn9</t>
+          <t>QP8QvjOG</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -488,7 +488,7 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>jiAoNQdE</t>
+          <t>MXB9rYOi</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -503,7 +503,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>842EOIGL</t>
+          <t>UwPNKUWp</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -518,7 +518,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>naHJ2yf2</t>
+          <t>Ia5ItCg4</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -533,11 +533,15 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>02sgHz9e</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
+          <t>4duqSCvB</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.182880957571713</v>
+      </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
@@ -548,7 +552,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>4zlpJdvq</t>
+          <t>CMriQj9N</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -563,7 +567,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>8Sp1FEw8</t>
+          <t>jFGHcfig</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -578,7 +582,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>dhkQFrkl</t>
+          <t>bXuieB8c</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -593,7 +597,7 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>x88gL4RQ</t>
+          <t>nucZxUhT</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -608,7 +612,7 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>vymauDyP</t>
+          <t>rPc4X7Gj</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
@@ -620,6 +624,160 @@
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
     </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>zeCiJHet</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>U5mYDMJ0</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.182880957571713</v>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>rsizUY9b</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>UaS8aGMt</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>QXtsC0lD</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>zHmSVfun</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>YFePBifU</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>dA00HeQh</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>4z48FZf5</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>02cHDDPH</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/spain/p6_deployment/data_preparation/df_emergency_fill.xlsx
+++ b/data/spain/p6_deployment/data_preparation/df_emergency_fill.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,7 +473,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>QP8QvjOG</t>
+          <t>zeCiJHet</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -488,11 +488,15 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>MXB9rYOi</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
+          <t>U5mYDMJ0</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.2560802151186845</v>
+      </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
@@ -503,7 +507,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>UwPNKUWp</t>
+          <t>rsizUY9b</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -518,7 +522,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>Ia5ItCg4</t>
+          <t>UaS8aGMt</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -533,15 +537,11 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>4duqSCvB</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>1</v>
-      </c>
-      <c r="C6" t="n">
-        <v>0.182880957571713</v>
-      </c>
+          <t>QXtsC0lD</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
@@ -552,7 +552,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>CMriQj9N</t>
+          <t>dA00HeQh</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -567,7 +567,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>jFGHcfig</t>
+          <t>4z48FZf5</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -582,7 +582,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>bXuieB8c</t>
+          <t>02cHDDPH</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -594,190 +594,6 @@
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
     </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>nucZxUhT</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>rPc4X7Gj</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>zeCiJHet</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>U5mYDMJ0</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>1</v>
-      </c>
-      <c r="C13" t="n">
-        <v>0.182880957571713</v>
-      </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>rsizUY9b</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>UaS8aGMt</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>QXtsC0lD</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>zHmSVfun</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr"/>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>YFePBifU</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>dA00HeQh</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>4z48FZf5</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr"/>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>02cHDDPH</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr"/>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/spain/p6_deployment/data_preparation/df_emergency_fill.xlsx
+++ b/data/spain/p6_deployment/data_preparation/df_emergency_fill.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,7 +461,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_hei_player_sub</t>
+          <t>dif_mean_wage_player_sub</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -473,7 +473,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>zeCiJHet</t>
+          <t>QP8QvjOG</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -488,15 +488,11 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>U5mYDMJ0</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C3" t="n">
-        <v>0.2560802151186845</v>
-      </c>
+          <t>CMriQj9N</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
@@ -507,7 +503,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>rsizUY9b</t>
+          <t>MXB9rYOi</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -522,7 +518,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>UaS8aGMt</t>
+          <t>Ia5ItCg4</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -537,11 +533,15 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>QXtsC0lD</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
+          <t>4duqSCvB</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" t="n">
+        <v>-0.01310954113289054</v>
+      </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
@@ -552,7 +552,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>dA00HeQh</t>
+          <t>UwPNKUWp</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -567,7 +567,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>4z48FZf5</t>
+          <t>jFGHcfig</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -582,7 +582,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>02cHDDPH</t>
+          <t>bXuieB8c</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -594,6 +594,36 @@
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
     </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>nucZxUhT</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>rPc4X7Gj</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/spain/p6_deployment/data_preparation/df_emergency_fill.xlsx
+++ b/data/spain/p6_deployment/data_preparation/df_emergency_fill.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,44 +436,44 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>dif_mean_last_180_matches_mean_rat_player_start_against</t>
+          <t>dif_mean_hei_player_sub</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_rat_player_sub</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_value_player_sub</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rep_player_sub</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_wage_player_sub</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_sub</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_age_player_sub</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_sub</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_value_player_sub</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_sub</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_wage_player_sub</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rep_player_sub</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>QP8QvjOG</t>
+          <t>IsCnpo0d</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -488,7 +488,7 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>CMriQj9N</t>
+          <t>buKPeYL5</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -503,7 +503,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>MXB9rYOi</t>
+          <t>vVwOqx6D</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -518,7 +518,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>Ia5ItCg4</t>
+          <t>C2KEmK6l</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -533,15 +533,11 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>4duqSCvB</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>1</v>
-      </c>
-      <c r="C6" t="n">
-        <v>-0.01310954113289054</v>
-      </c>
+          <t>SCX7iT7M</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
@@ -552,7 +548,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>UwPNKUWp</t>
+          <t>QP8QvjOG</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -567,7 +563,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>jFGHcfig</t>
+          <t>CMriQj9N</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -582,7 +578,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>bXuieB8c</t>
+          <t>MXB9rYOi</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -597,7 +593,7 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>nucZxUhT</t>
+          <t>Ia5ItCg4</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -612,7 +608,7 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>rPc4X7Gj</t>
+          <t>4duqSCvB</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
@@ -624,6 +620,66 @@
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
     </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>UwPNKUWp</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>bXuieB8c</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>nucZxUhT</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>rPc4X7Gj</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
